--- a/data_processed/results_OLS_m3_gas_per_capitaincome.xlsx
+++ b/data_processed/results_OLS_m3_gas_per_capitaincome.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>455.135860177068</v>
+        <v>455.1358601770683</v>
       </c>
       <c r="D2" t="n">
-        <v>1.98542922306122e-88</v>
+        <v>1.985429223062402e-88</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>3.077449507152737</v>
+        <v>3.077449507152742</v>
       </c>
       <c r="D3" t="n">
-        <v>7.803805975391543e-09</v>
+        <v>7.803805975392066e-09</v>
       </c>
     </row>
     <row r="4">
@@ -483,14 +483,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>building_type</t>
+          <t>household_size</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-55.05572393278808</v>
+        <v>-115.2295524845276</v>
       </c>
       <c r="D4" t="n">
-        <v>1.238117694329613e-133</v>
+        <v>1.072434276257687e-149</v>
       </c>
     </row>
     <row r="5">
@@ -499,11 +499,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>building_age</t>
+          <t>dwelling_size</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38.44262490551083</v>
+        <v>5.48202841324462</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -515,14 +515,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>population_density</t>
+          <t>building_type</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.1541528326211498</v>
+        <v>-55.0557239327881</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6724372927615693</v>
+        <v>1.238117694329354e-133</v>
       </c>
     </row>
     <row r="7">
@@ -531,14 +531,14 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>household_size</t>
+          <t>building_age</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-115.2295524845275</v>
+        <v>38.44262490551083</v>
       </c>
       <c r="D7" t="n">
-        <v>1.072434276257044e-149</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -547,14 +547,14 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>dwelling_size</t>
+          <t>population_density</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.482028413244621</v>
+        <v>-0.1541528326211276</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>0.6724372927615729</v>
       </c>
     </row>
     <row r="9">
@@ -567,10 +567,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-375.6298042356195</v>
+        <v>-375.6298042356198</v>
       </c>
       <c r="D9" t="n">
-        <v>5.916528750765869e-73</v>
+        <v>5.916528750765214e-73</v>
       </c>
     </row>
     <row r="10">
@@ -583,10 +583,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-760.5957781391785</v>
+        <v>-760.5957781391787</v>
       </c>
       <c r="D10" t="n">
-        <v>2.234209591842669e-220</v>
+        <v>2.23420959184492e-220</v>
       </c>
     </row>
   </sheetData>
